--- a/companies/gigadevice/financial-model.xlsx
+++ b/companies/gigadevice/financial-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R2aefe0034dc54562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical" sheetId="2" r:id="Rbea0eae891b94a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="3" r:id="R9e693a42f8674e96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" r:id="Rc46c5c3bc14241ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" r:id="R2e0c1b865559464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="R1c38dceb1ecf4e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources Audit" sheetId="7" r:id="R10dc3218e59d4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rf1111c30c6af47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical" sheetId="2" r:id="R06d92b7cc6554c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="3" r:id="R4630783be0ae4549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" r:id="R1b4505f5a3484329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" r:id="R601de9a854584b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="Rad3ff96d68454dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources Audit" sheetId="7" r:id="R2e105b2f9a40463a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -94,7 +94,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="12">
+  <x:numFmts count="13">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="&quot;RMB &quot;0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.00&quot; m&quot;"/>
@@ -107,8 +107,9 @@
     <x:numFmt numFmtId="209" formatCode="&quot;RMB &quot;0"/>
     <x:numFmt numFmtId="210" formatCode="0.0000"/>
     <x:numFmt numFmtId="211" formatCode="0.000"/>
+    <x:numFmt numFmtId="212" formatCode="0.000&quot; bn&quot;"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -168,8 +169,13 @@
       <x:color rgb="FF0563C1"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -204,6 +210,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -279,7 +295,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="154">
+  <x:cellXfs count="173">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -468,6 +484,45 @@
     <x:xf numFmtId="211" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="212" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="212" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -478,7 +533,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -488,7 +543,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -828,7 +883,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfabd8688a267493e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re34b689b2d00408a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -858,7 +913,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf5d73d8781734c96"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbeda31a4eb3d4fb0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1141,19 +1196,19 @@
       </x:c>
       <x:c r="J3" t="n">
         <x:f>'Assumptions'!B4</x:f>
-        <x:v>393</x:v>
+        <x:v>326.46</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
         <x:v>价格基准</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="n">
-        <x:v>46266</x:v>
+      <x:c r="B4" s="13" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J4" t="n">
         <x:f>'Assumptions'!B4</x:f>
-        <x:v>393</x:v>
+        <x:v>326.46</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1161,11 +1216,11 @@
         <x:v>资料截止</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-10-12交易时段</x:v>
       </x:c>
       <x:c r="J5" t="n">
         <x:f>'Assumptions'!B4</x:f>
-        <x:v>393</x:v>
+        <x:v>326.46</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1181,7 +1236,7 @@
         <x:v>模型版本</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>首次建档 / 2026H1 v1.0</x:v>
+        <x:v>增量更新 / 2027正常化 v1.1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1194,11 +1249,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>模型状态</x:v>
+        <x:v>最新财报</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:f>'Checks'!F2</x:f>
-        <x:v>OK</x:v>
+        <x:v>2026H1；未检索到Q3</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1206,7 +1260,7 @@
         <x:v>当前判断</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
-        <x:v>中性观察；业务质量高，盈利可见度中低</x:v>
+        <x:v>中性偏积极；业务质量高，盈利可见度中低</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1226,34 +1280,34 @@
       </x:c>
       <x:c r="B13" s="40" t="n">
         <x:f>'Assumptions'!B4</x:f>
-        <x:v>393</x:v>
+        <x:v>326.46</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>2026-09-01 收盘</x:v>
+        <x:v>2026-10-09收盘</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>经济股数</x:v>
+        <x:v>保守摊薄股数</x:v>
       </x:c>
       <x:c r="B14" s="41" t="n">
         <x:f>'Assumptions'!B8</x:f>
-        <x:v>702.309127</x:v>
+        <x:v>705.4593269999999</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>总股本扣除已回购拟注销股份</x:v>
+        <x:v>总股本+已授予H股奖励压力</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>经济市值</x:v>
+        <x:v>A价等值市值</x:v>
       </x:c>
       <x:c r="B15" s="42" t="n">
         <x:f>'Assumptions'!B9</x:f>
-        <x:v>276.007486911</x:v>
+        <x:v>230.30425189241996</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>价格×经济股数</x:v>
+        <x:v>非真实A+H市值合计</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1298,10 +1352,10 @@
       </x:c>
       <x:c r="B19" s="44" t="n">
         <x:f>'Valuation'!F5</x:f>
-        <x:v>249.17802328375552</x:v>
+        <x:v>201.28729547578865</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>周期快速回落</x:v>
+        <x:v>2027毛利回归</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1310,10 +1364,10 @@
       </x:c>
       <x:c r="B20" s="44" t="n">
         <x:f>'Valuation'!F6</x:f>
-        <x:v>447.0965674919956</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>高景气部分延续</x:v>
+        <x:v>2027部分高景气延续</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1322,10 +1376,10 @@
       </x:c>
       <x:c r="B21" s="44" t="n">
         <x:f>'Valuation'!F7</x:f>
-        <x:v>645.0151117002357</x:v>
+        <x:v>642.1348228910723</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>紧供给延续至2027</x:v>
+        <x:v>2027紧供给及新品持续</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1334,7 +1388,7 @@
       </x:c>
       <x:c r="B22" s="45" t="n">
         <x:f>'Valuation'!G6</x:f>
-        <x:v>0.1376502989618209</x:v>
+        <x:v>0.16802012029571922</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
         <x:v>情景差异，不是收益保证</x:v>
@@ -1346,7 +1400,7 @@
       </x:c>
       <x:c r="B23" s="46" t="n">
         <x:f>('Assumptions'!B9-'Assumptions'!B24)/'Assumptions'!B22</x:f>
-        <x:v>26.2007486911</x:v>
+        <x:v>25.447559046167054</x:v>
       </x:c>
       <x:c r="C23" s="16" t="str">
         <x:v>当前市值扣基准投资价值</x:v>
@@ -1380,7 +1434,7 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="49" t="str">
-        <x:v>2026H1收入115.66亿元、扣非净利润48.83亿元，存储器收入同比增长245%、毛利率升至67.57%，盈利拐点极强。但归母净利润还包含19.74亿元非经常损益，且存储器占收入约85%，静态P/E会同时放大投资收益和周期峰值。模型用正常化扣非利润加折价金融投资估值：Bear/Base/Bull为249.18/447.10/645.02元。393元对应基准上行13.8%，安全边际有限，结论为中性观察；首要跟踪存储ASP、毛利率、库存与现金转换。</x:v>
+        <x:v>2026H1收入115.66亿元、扣非利润48.83亿元，存储占收入85%、毛利率67.57%。代工涨价与大额投资收益要求保守正常化：主估值移至2027，利润60/85/115亿元，计入已授予H股奖励压力股本，未提前扣减拟注销回购。参考价326.46元，Base约381.31元、空间16.8%；结论中性偏积极。采购预算不等于订单，现金流需关注19.46亿元经营性应付增加。</x:v>
       </x:c>
       <x:c r="B27" s="49" t="str">
         <x:v>2026H1收入115.66亿元、扣非净利润48.83亿元，存储器收入同比增长245%、毛利率升至67.57%，盈利拐点极强。但归母净利润还包含19.74亿元非经常损益，且存储器占收入约85%，静态P/E会同时放大投资收益和周期峰值。模型用正常化扣非利润加折价金融投资估值：Bear/Base/Bull为249.18/447.10/645.02元。393元对应基准上行13.8%，安全边际有限，结论为中性观察；首要跟踪存储ASP、毛利率、库存与现金转换。</x:v>
@@ -1541,7 +1595,7 @@
     <x:mergeCell ref="A27:H32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb127e674fd684557"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20eaa558b65d4b5a"/>
 </x:worksheet>
 </file>
 
@@ -1920,9 +1974,100 @@
         <x:v>H1-Q1研究计算</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="156" t="str">
+        <x:v>2026H1补充现金质量（十亿元人民币；S1 p55/143/147）</x:v>
+      </x:c>
+      <x:c r="B19" s="156"/>
+      <x:c r="C19" s="156"/>
+      <x:c r="D19" s="156"/>
+      <x:c r="E19" s="156"/>
+      <x:c r="F19" s="156"/>
+      <x:c r="G19" s="156"/>
+    </x:row>
+    <x:row r="20" ht="23" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>现金资本开支</x:v>
+      </x:c>
+      <x:c r="F20" s="162" t="n">
+        <x:v>0.94510542708</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="23" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>简化自由现金流</x:v>
+      </x:c>
+      <x:c r="F21" s="163" t="n">
+        <x:f>F7-F20</x:f>
+        <x:v>5.10323557292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="23" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>经营性应付增加</x:v>
+      </x:c>
+      <x:c r="F22" s="162" t="n">
+        <x:v>1.9464313616</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="23" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>经营性应收占款</x:v>
+      </x:c>
+      <x:c r="F23" s="162" t="n">
+        <x:v>0.130666393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="23" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>存货现金占款</x:v>
+      </x:c>
+      <x:c r="F24" s="162" t="n">
+        <x:v>1.20318996434</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="23" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>本期资本化研发新增</x:v>
+      </x:c>
+      <x:c r="F25" s="162" t="n">
+        <x:v>0.20089620902</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="167" t="str">
+        <x:v>现金流调节表存货占款1.203bn不等于存货净额增加1.118bn；经营性应付增加1.946bn不只含应付账款。CFO/扣非123.9%须结合营运资本和研发资本化观察。</x:v>
+      </x:c>
+      <x:c r="B27" s="167"/>
+      <x:c r="C27" s="167"/>
+      <x:c r="D27" s="167"/>
+      <x:c r="E27" s="167"/>
+      <x:c r="F27" s="167"/>
+      <x:c r="G27" s="167"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="167"/>
+      <x:c r="B28" s="167"/>
+      <x:c r="C28" s="167"/>
+      <x:c r="D28" s="167"/>
+      <x:c r="E28" s="167"/>
+      <x:c r="F28" s="167"/>
+      <x:c r="G28" s="167"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="167"/>
+      <x:c r="B29" s="167"/>
+      <x:c r="C29" s="167"/>
+      <x:c r="D29" s="167"/>
+      <x:c r="E29" s="167"/>
+      <x:c r="F29" s="167"/>
+      <x:c r="G29" s="167"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A19:G19"/>
+    <x:mergeCell ref="A27:G29"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2205,14 +2350,14 @@
         <x:v>货币资金</x:v>
       </x:c>
       <x:c r="H11" s="65" t="n">
-        <x:v>7.776</x:v>
+        <x:v>9.18626998261</x:v>
       </x:c>
       <x:c r="I11" s="65" t="n">
         <x:v>16.964598</x:v>
       </x:c>
       <x:c r="J11" s="86" t="n">
         <x:f>IF(H11=0,"",I11/H11-1)</x:f>
-        <x:v>1.1816612654320986</x:v>
+        <x:v>0.846734096876611</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2220,7 +2365,7 @@
         <x:v>产品</x:v>
       </x:c>
       <x:c r="B12" s="20" t="str">
-        <x:v>2025A收入</x:v>
+        <x:v>2025收入</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
         <x:v>收入占比</x:v>
@@ -2447,7 +2592,7 @@
         <x:v>市场、股份与估值假设</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="19" t="str">
         <x:v>市场与股份</x:v>
       </x:c>
@@ -2457,95 +2602,170 @@
       <x:c r="C3" s="21" t="str">
         <x:v>说明</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="D3" s="156" t="str">
+        <x:v>股份压力输入</x:v>
+      </x:c>
+      <x:c r="E3" s="156" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="F3" s="156" t="str">
+        <x:v>口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="11" t="str">
         <x:v>A股收盘价</x:v>
       </x:c>
       <x:c r="B4" s="101" t="n">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>2026-09-01收盘</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>326.46</x:v>
+      </x:c>
+      <x:c r="C4" s="148" t="str">
+        <x:v>2026-10-09收盘；S12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>行权后总股本</x:v>
+        <x:v>已发行A+H总股本</x:v>
       </x:c>
       <x:c r="B5" s="102" t="n">
         <x:v>703.971427</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>期权行权后；百万股</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="C5" s="150" t="str">
+        <x:v>703,971,427股；S11</x:v>
+      </x:c>
+      <x:c r="D5" s="143" t="str">
+        <x:v>已授予H股奖励</x:v>
+      </x:c>
+      <x:c r="E5" s="159" t="n">
+        <x:v>1.4879</x:v>
+      </x:c>
+      <x:c r="F5" s="143" t="str">
+        <x:v>百万股；待接受及归属；S9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="14" t="str">
         <x:v>已回购拟注销股份</x:v>
       </x:c>
       <x:c r="B6" s="102" t="n">
-        <x:v>1.6623</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>截至2026-08-31；百万股</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>2.6139</x:v>
+      </x:c>
+      <x:c r="C6" s="150" t="str">
+        <x:v>截至10月8日；S7+S10，未注销</x:v>
+      </x:c>
+      <x:c r="D6" s="143" t="str">
+        <x:v>全部回购注销情景</x:v>
+      </x:c>
+      <x:c r="E6" s="157" t="n">
+        <x:f>B8-B6</x:f>
+        <x:v>702.845427</x:v>
+      </x:c>
+      <x:c r="F6" s="143" t="str">
+        <x:v>只作敏感性，不当已完成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="14" t="str">
         <x:v>H股股本</x:v>
       </x:c>
       <x:c r="B7" s="102" t="n">
         <x:v>33.2531</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="str">
+      <x:c r="C7" s="150" t="str">
         <x:v>百万股；不单独折价</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
+      <x:c r="D7" s="143" t="str">
+        <x:v>注销对每股价值影响</x:v>
+      </x:c>
+      <x:c r="E7" s="158" t="n">
+        <x:f>B8/E6-1</x:f>
+        <x:v>0.003719025406705656</x:v>
+      </x:c>
+      <x:c r="F7" s="143" t="str">
+        <x:v>股份变化，利润不变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>经济股数</x:v>
+        <x:v>保守摊薄股数</x:v>
       </x:c>
       <x:c r="B8" s="102" t="n">
-        <x:f>B5-B6</x:f>
-        <x:v>702.309127</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>用于每股价值分母</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:f>B5+E5</x:f>
+        <x:v>705.4593269999999</x:v>
+      </x:c>
+      <x:c r="C8" s="150" t="str">
+        <x:v>总股本+已授予H股奖励压力</x:v>
+      </x:c>
+      <x:c r="D8" s="143" t="str">
+        <x:v>模型奖励口径</x:v>
+      </x:c>
+      <x:c r="E8" s="157" t="str">
+        <x:v>全额新增压力</x:v>
+      </x:c>
+      <x:c r="F8" s="143" t="str">
+        <x:v>不声称已发行或已归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>经济市值</x:v>
+        <x:v>A价等值市值</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
         <x:f>B4*B8/1000</x:f>
-        <x:v>276.007486911</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>十亿元</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>230.30425189241996</x:v>
+      </x:c>
+      <x:c r="C9" s="150" t="str">
+        <x:v>A价×摊薄股数，非真实A+H合计市值</x:v>
+      </x:c>
+      <x:c r="D9" s="143" t="str">
+        <x:v>H股奖励计划总授权</x:v>
+      </x:c>
+      <x:c r="E9" s="159" t="n">
+        <x:v>70.397142</x:v>
+      </x:c>
+      <x:c r="F9" s="143" t="str">
+        <x:v>百万股；含已授予部分，S9 p4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="14" t="str">
         <x:v>金融投资账面值</x:v>
       </x:c>
       <x:c r="B10" s="66" t="n">
         <x:v>16.02</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="str">
+      <x:c r="C10" s="150" t="str">
         <x:v>四类金融投资合计</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11">
+      <x:c r="D10" s="143" t="str">
+        <x:v>剩余未授予额度</x:v>
+      </x:c>
+      <x:c r="E10" s="157" t="n">
+        <x:f>E9-E5</x:f>
+        <x:v>68.909242</x:v>
+      </x:c>
+      <x:c r="F10" s="143" t="str">
+        <x:v>非确定新增股份</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>2026H1扣非净利润</x:v>
       </x:c>
       <x:c r="B11" s="93" t="n">
         <x:v>4.883033</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="str">
+      <x:c r="C11" s="152" t="str">
         <x:v>排除非经常损益</x:v>
+      </x:c>
+      <x:c r="D11" s="143" t="str">
+        <x:v>计划额度依据</x:v>
+      </x:c>
+      <x:c r="E11" s="143" t="str">
+        <x:v>全部已发行股数10%</x:v>
+      </x:c>
+      <x:c r="F11" s="143" t="str">
+        <x:v>不只按现有H股计算</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2567,13 +2787,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
-        <x:v>2026E核心净利润</x:v>
+        <x:v>2027E正常化核心利润</x:v>
       </x:c>
       <x:c r="B15" s="109" t="n">
-        <x:v>7.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="D15" s="109" t="n">
         <x:v>11.5</x:v>
@@ -2621,13 +2841,13 @@
         <x:v>核心逻辑</x:v>
       </x:c>
       <x:c r="B18" s="16" t="str">
-        <x:v>周期快速回落</x:v>
+        <x:v>毛利回归与成本上升</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
-        <x:v>高景气部分延续</x:v>
+        <x:v>部分高景气延续</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
-        <x:v>紧供给延续至2027</x:v>
+        <x:v>紧供给及新品持续</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
         <x:v>研究假设</x:v>
@@ -2653,13 +2873,13 @@
       </x:c>
       <x:c r="B22" s="11" t="n">
         <x:f>C15</x:f>
-        <x:v>10</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>H1核心4.883；H2隐含5.117</x:v>
+        <x:v>2027正常化；不年化H1或Q2</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2706,12 +2926,80 @@
         <x:v>避免与利润中的资金收益重复</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="156" t="str">
+        <x:v>2026近期盈利假设保留为观察，主估值移至2027</x:v>
+      </x:c>
+      <x:c r="B28" s="156"/>
+      <x:c r="C28" s="156"/>
+      <x:c r="D28" s="156"/>
+      <x:c r="E28" s="156"/>
+      <x:c r="F28" s="156"/>
+    </x:row>
+    <x:row r="29" ht="25" customHeight="1">
+      <x:c r="A29" s="143" t="str">
+        <x:v>参考年份</x:v>
+      </x:c>
+      <x:c r="B29" s="143" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C29" s="143" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="D29" s="143" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="E29" s="143" t="str">
+        <x:v>性质</x:v>
+      </x:c>
+      <x:c r="F29" s="143"/>
+    </x:row>
+    <x:row r="30" ht="25" customHeight="1">
+      <x:c r="A30" s="143" t="str">
+        <x:v>2026E核心利润</x:v>
+      </x:c>
+      <x:c r="B30" s="160" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="C30" s="160" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D30" s="160" t="n">
+        <x:v>11.5</x:v>
+      </x:c>
+      <x:c r="E30" s="143" t="str">
+        <x:v>十亿元；原假设，非新增披露</x:v>
+      </x:c>
+      <x:c r="F30" s="143"/>
+    </x:row>
+    <x:row r="31" ht="25" customHeight="1">
+      <x:c r="A31" s="143" t="str">
+        <x:v>2027E核心利润</x:v>
+      </x:c>
+      <x:c r="B31" s="160" t="n">
+        <x:f>B15</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C31" s="160" t="n">
+        <x:f>C15</x:f>
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="D31" s="160" t="n">
+        <x:f>D15</x:f>
+        <x:v>11.5</x:v>
+      </x:c>
+      <x:c r="E31" s="143" t="str">
+        <x:v>十亿元；本次主估值</x:v>
+      </x:c>
+      <x:c r="F31" s="143"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A28:F28"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fbf05970d44250"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37f692cff13a4621"/>
 </x:worksheet>
 </file>
 
@@ -2730,7 +3018,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>正常化核心利润 + 折价金融投资估值</x:v>
+        <x:v>2027正常化核心利润 + 折价金融投资估值</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
         <x:v>正常化核心利润 + 折价金融投资估值</x:v>
@@ -2780,7 +3068,7 @@
       </x:c>
       <x:c r="B5" s="109" t="n">
         <x:f>'Assumptions'!B15</x:f>
-        <x:v>7.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="122" t="n">
         <x:f>'Assumptions'!B16</x:f>
@@ -2792,15 +3080,15 @@
       </x:c>
       <x:c r="E5" s="109" t="n">
         <x:f>B5*C5+D5</x:f>
-        <x:v>175</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F5" s="40" t="n">
         <x:f>E5/'Assumptions'!$B$8*1000</x:f>
-        <x:v>249.17802328375552</x:v>
+        <x:v>201.28729547578865</x:v>
       </x:c>
       <x:c r="G5" s="86" t="n">
         <x:f>F5/'Assumptions'!$B$4-1</x:f>
-        <x:v>-0.36595922828560934</x:v>
+        <x:v>-0.38342432311527086</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2809,7 +3097,7 @@
       </x:c>
       <x:c r="B6" s="124" t="n">
         <x:f>'Assumptions'!C15</x:f>
-        <x:v>10</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="C6" s="125" t="n">
         <x:f>'Assumptions'!C16</x:f>
@@ -2821,15 +3109,15 @@
       </x:c>
       <x:c r="E6" s="124" t="n">
         <x:f>B6*C6+D6</x:f>
-        <x:v>314</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F6" s="126" t="n">
         <x:f>E6/'Assumptions'!$B$8*1000</x:f>
-        <x:v>447.0965674919956</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="G6" s="127" t="n">
         <x:f>F6/'Assumptions'!$B$4-1</x:f>
-        <x:v>0.1376502989618209</x:v>
+        <x:v>0.16802012029571922</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2854,11 +3142,11 @@
       </x:c>
       <x:c r="F7" s="130" t="n">
         <x:f>E7/'Assumptions'!$B$8*1000</x:f>
-        <x:v>645.0151117002357</x:v>
+        <x:v>642.1348228910723</x:v>
       </x:c>
       <x:c r="G7" s="95" t="n">
         <x:f>F7/'Assumptions'!$B$4-1</x:f>
-        <x:v>0.6412598262092513</x:v>
+        <x:v>0.9669632509069177</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2889,19 +3177,19 @@
         <x:v>利润 \ P/E</x:v>
       </x:c>
       <x:c r="B12" s="53" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="53" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D12" s="53" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E12" s="53" t="n">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F12" s="53" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="54" t="str">
         <x:v>说明</x:v>
@@ -2909,55 +3197,55 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="109" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B13" s="133" t="n">
         <x:f>($A13*B$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>293.3181302654493</x:v>
+        <x:v>206.9573601370785</x:v>
       </x:c>
       <x:c r="C13" s="133" t="n">
         <x:f>($A13*C$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>327.49111631579296</x:v>
+        <x:v>240.97774810481744</x:v>
       </x:c>
       <x:c r="D13" s="133" t="n">
         <x:f>($A13*D$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>361.66410236613655</x:v>
+        <x:v>274.99813607255635</x:v>
       </x:c>
       <x:c r="E13" s="133" t="n">
         <x:f>($A13*E$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>395.8370884164802</x:v>
+        <x:v>309.0185240402953</x:v>
       </x:c>
       <x:c r="F13" s="133" t="n">
         <x:f>($A13*F$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>430.01007446682377</x:v>
+        <x:v>343.03891200803423</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>较弱</x:v>
+        <x:v>Bear利润</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="111" t="n">
-        <x:v>9</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="B14" s="134" t="n">
         <x:f>($A14*B$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>327.49111631579296</x:v>
+        <x:v>253.7353935927195</x:v>
       </x:c>
       <x:c r="C14" s="134" t="n">
         <x:f>($A14*C$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>365.9357256224295</x:v>
+        <x:v>296.2608785523932</x:v>
       </x:c>
       <x:c r="D14" s="134" t="n">
         <x:f>($A14*D$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>404.38033492906607</x:v>
+        <x:v>338.7863635120668</x:v>
       </x:c>
       <x:c r="E14" s="134" t="n">
         <x:f>($A14*E$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>442.8249442357026</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="F14" s="134" t="n">
         <x:f>($A14*F$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>481.26955354233917</x:v>
+        <x:v>423.83733343141415</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
         <x:v>偏弱</x:v>
@@ -2965,27 +3253,27 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="111" t="n">
-        <x:v>10</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="B15" s="134" t="n">
         <x:f>($A15*B$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>361.66410236613655</x:v>
+        <x:v>284.9207492298135</x:v>
       </x:c>
       <x:c r="C15" s="134" t="n">
         <x:f>($A15*C$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>404.38033492906607</x:v>
+        <x:v>333.116298850777</x:v>
       </x:c>
       <x:c r="D15" s="134" t="n">
         <x:f>($A15*D$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>447.0965674919956</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="E15" s="134" t="n">
         <x:f>($A15*E$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>489.8128000549251</x:v>
+        <x:v>429.507398092704</x:v>
       </x:c>
       <x:c r="F15" s="134" t="n">
         <x:f>($A15*F$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>532.5290326178547</x:v>
+        <x:v>477.70294771366747</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
         <x:v>Base利润</x:v>
@@ -2993,55 +3281,55 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="111" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="134" t="n">
         <x:f>($A16*B$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>395.8370884164802</x:v>
+        <x:v>331.69878268545455</x:v>
       </x:c>
       <x:c r="C16" s="134" t="n">
         <x:f>($A16*C$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>442.8249442357026</x:v>
+        <x:v>388.39942929835274</x:v>
       </x:c>
       <x:c r="D16" s="134" t="n">
         <x:f>($A16*D$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>489.8128000549251</x:v>
+        <x:v>445.100075911251</x:v>
       </x:c>
       <x:c r="E16" s="134" t="n">
         <x:f>($A16*E$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>536.8006558741477</x:v>
+        <x:v>501.8007225241492</x:v>
       </x:c>
       <x:c r="F16" s="134" t="n">
         <x:f>($A16*F$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>583.7885116933701</x:v>
+        <x:v>558.5013691370474</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>偏强</x:v>
+        <x:v>近年高景气</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="128" t="n">
-        <x:v>12</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="B17" s="135" t="n">
         <x:f>($A17*B$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>430.01007446682377</x:v>
+        <x:v>378.4768161410956</x:v>
       </x:c>
       <x:c r="C17" s="135" t="n">
         <x:f>($A17*C$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>481.26955354233917</x:v>
+        <x:v>443.68255974592853</x:v>
       </x:c>
       <x:c r="D17" s="135" t="n">
         <x:f>($A17*D$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>532.5290326178547</x:v>
+        <x:v>508.88830335076153</x:v>
       </x:c>
       <x:c r="E17" s="135" t="n">
         <x:f>($A17*E$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>583.7885116933701</x:v>
+        <x:v>574.0940469555944</x:v>
       </x:c>
       <x:c r="F17" s="135" t="n">
         <x:f>($A17*F$12+'Assumptions'!$C$17)/'Assumptions'!$B$8*1000</x:f>
-        <x:v>635.0479907688854</x:v>
+        <x:v>639.2997905604274</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str">
         <x:v>强景气</x:v>
@@ -3072,7 +3360,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="49" t="str">
-        <x:v>核心利润、估值倍数和金融投资折价均为研究假设，不是公司指引或一致预期。模型不按2026H1表观净利润年化，避免把19.74亿元非经常损益和存储器67.57%高毛利直接资本化。金融投资按账面值以内计入，不额外加回净现金，以降低与核心利润中利息收益重复计算的风险。</x:v>
+        <x:v>2027核心利润、P/E及投资折价为研究假设，非公司指引。2026H1非经常损益19.74亿元及存储67.57%毛利不直接永续化；核心利润含正常股份支付费用，不另加净现金。分母703.971427m+已授予1.4879m压力，未将回购当作已注销。新增采购预算含代工涨价，不能当作销售或利润保证。</x:v>
       </x:c>
       <x:c r="B21" s="49" t="str">
         <x:v>核心利润、估值倍数和金融投资折价均为研究假设，不是公司指引或一致预期。模型不按2026H1表观净利润年化，避免把19.74亿元非经常损益和存储器67.57%高毛利直接资本化。金融投资按账面值以内计入，不额外加回净现金，以降低与核心利润中利息收益重复计算的风险。</x:v>
@@ -3184,6 +3472,81 @@
       <x:c r="G25" s="49" t="str">
         <x:v>核心利润、估值倍数和金融投资折价均为研究假设，不是公司指引或一致预期。模型不按2026H1表观净利润年化，避免把19.74亿元非经常损益和存储器67.57%高毛利直接资本化。金融投资按账面值以内计入，不额外加回净现金，以降低与核心利润中利息收益重复计算的风险。</x:v>
       </x:c>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="156" t="str">
+        <x:v>股本、计划授权与周期风险（研究压力测试）</x:v>
+      </x:c>
+      <x:c r="B27" s="156"/>
+      <x:c r="C27" s="156"/>
+      <x:c r="D27" s="156"/>
+      <x:c r="E27" s="156"/>
+      <x:c r="F27" s="156"/>
+      <x:c r="G27" s="156"/>
+    </x:row>
+    <x:row r="28" ht="23" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>授权全部新增股数</x:v>
+      </x:c>
+      <x:c r="B28" s="96" t="n">
+        <x:f>'Assumptions'!B5+'Assumptions'!E9</x:f>
+        <x:v>774.368569</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>百万股；非Base</x:v>
+      </x:c>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+    </x:row>
+    <x:row r="29" ht="23" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>Base全授权价值</x:v>
+      </x:c>
+      <x:c r="B29" s="22" t="n">
+        <x:f>E6/B28*1000</x:f>
+        <x:v>347.37980177498656</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>利润和投资不变</x:v>
+      </x:c>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+    </x:row>
+    <x:row r="30" ht="23" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>Base回购全注销价值</x:v>
+      </x:c>
+      <x:c r="B30" s="22" t="n">
+        <x:f>E6/'Assumptions'!E6*1000</x:f>
+        <x:v>382.72995692408483</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>只减已实际回购</x:v>
+      </x:c>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+    </x:row>
+    <x:row r="31" ht="23" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>当前价隐含核心利润</x:v>
+      </x:c>
+      <x:c r="B31" s="24" t="n">
+        <x:f>('Assumptions'!B9-'Assumptions'!C17)/'Assumptions'!C16</x:f>
+        <x:v>7.210141729747332</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>十亿元，按Base P/E</x:v>
+      </x:c>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3191,6 +3554,7 @@
     <x:mergeCell ref="A11:G11"/>
     <x:mergeCell ref="A20:G20"/>
     <x:mergeCell ref="A21:G25"/>
+    <x:mergeCell ref="A27:G27"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B13:F17">
     <x:cfRule type="colorScale" priority="1">
@@ -3261,7 +3625,7 @@
         <x:v>总体模型状态</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:f>IF(COUNTIF(F5:F15,"FAIL")=0,"OK","FAIL")</x:f>
+        <x:f>IF(COUNTIF(F5:F15,"FAIL")+COUNTIF(F18:F21,"FAIL")=0,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
@@ -3430,15 +3794,15 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>经济股数桥</x:v>
+        <x:v>保守摊薄股数桥</x:v>
       </x:c>
       <x:c r="B10" s="139" t="n">
         <x:f>'Assumptions'!B8</x:f>
-        <x:v>702.309127</x:v>
+        <x:v>705.4593269999999</x:v>
       </x:c>
       <x:c r="C10" s="139" t="n">
-        <x:f>'Assumptions'!B5-'Assumptions'!B6</x:f>
-        <x:v>702.309127</x:v>
+        <x:f>'Assumptions'!B5+'Assumptions'!E5</x:f>
+        <x:v>705.4593269999999</x:v>
       </x:c>
       <x:c r="D10" s="139" t="n">
         <x:f>B10-C10</x:f>
@@ -3453,20 +3817,20 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>总股本减拟注销股份</x:v>
+        <x:v>总股本加已授予H股奖励压力</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>经济市值桥</x:v>
+        <x:v>A价等值市值桥</x:v>
       </x:c>
       <x:c r="B11" s="139" t="n">
         <x:f>'Assumptions'!B9</x:f>
-        <x:v>276.007486911</x:v>
+        <x:v>230.30425189241996</x:v>
       </x:c>
       <x:c r="C11" s="139" t="n">
         <x:f>'Assumptions'!B4*'Assumptions'!B8/1000</x:f>
-        <x:v>276.007486911</x:v>
+        <x:v>230.30425189241996</x:v>
       </x:c>
       <x:c r="D11" s="139" t="n">
         <x:f>B11-C11</x:f>
@@ -3481,7 +3845,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>价格×经济股数</x:v>
+        <x:v>A价×压力股本，不是A+H实市值</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3490,11 +3854,11 @@
       </x:c>
       <x:c r="B12" s="139" t="n">
         <x:f>'Valuation'!E6</x:f>
-        <x:v>314</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C12" s="139" t="n">
         <x:f>'Assumptions'!C15*'Assumptions'!C16+'Assumptions'!C17</x:f>
-        <x:v>314</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D12" s="139" t="n">
         <x:f>B12-C12</x:f>
@@ -3518,11 +3882,11 @@
       </x:c>
       <x:c r="B13" s="139" t="n">
         <x:f>'Valuation'!F6</x:f>
-        <x:v>447.0965674919956</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="C13" s="139" t="n">
         <x:f>'Valuation'!E6/'Assumptions'!B8*1000</x:f>
-        <x:v>447.0965674919956</x:v>
+        <x:v>381.31184847174046</x:v>
       </x:c>
       <x:c r="D13" s="139" t="n">
         <x:f>B13-C13</x:f>
@@ -3537,7 +3901,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>权益价值/经济股数</x:v>
+        <x:v>权益价值/保守摊薄股数</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3546,7 +3910,7 @@
       </x:c>
       <x:c r="B14" s="139" t="n">
         <x:f>'Valuation'!F7-'Valuation'!F5</x:f>
-        <x:v>395.8370884164802</x:v>
+        <x:v>440.84752741528365</x:v>
       </x:c>
       <x:c r="C14" s="139" t="n">
         <x:f>0</x:f>
@@ -3554,7 +3918,7 @@
       </x:c>
       <x:c r="D14" s="139" t="n">
         <x:f>B14-C14</x:f>
-        <x:v>395.8370884164802</x:v>
+        <x:v>440.84752741528365</x:v>
       </x:c>
       <x:c r="E14" s="139" t="n">
         <x:f>0</x:f>
@@ -3574,7 +3938,7 @@
       </x:c>
       <x:c r="B15" s="140" t="n">
         <x:f>MIN('Assumptions'!B4,'Assumptions'!B8,'Assumptions'!B15,'Assumptions'!C15,'Assumptions'!D15)</x:f>
-        <x:v>7.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="140" t="n">
         <x:f>0</x:f>
@@ -3582,7 +3946,7 @@
       </x:c>
       <x:c r="D15" s="140" t="n">
         <x:f>B15-C15</x:f>
-        <x:v>7.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="140" t="n">
         <x:f>0</x:f>
@@ -3594,6 +3958,133 @@
       </x:c>
       <x:c r="G15" s="16" t="str">
         <x:v>核心输入必须大于0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="19" t="str">
+        <x:v>检查项</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>实际值</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>预期/阈值</x:v>
+      </x:c>
+      <x:c r="D17" s="20" t="str">
+        <x:v>差异</x:v>
+      </x:c>
+      <x:c r="E17" s="20" t="str">
+        <x:v>容差</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>股本来源核对</x:v>
+      </x:c>
+      <x:c r="B18" s="136" t="n">
+        <x:f>'Assumptions'!B8</x:f>
+        <x:v>705.4593269999999</x:v>
+      </x:c>
+      <x:c r="C18" s="136" t="n">
+        <x:v>705.459327</x:v>
+      </x:c>
+      <x:c r="D18" s="136" t="n">
+        <x:f>B18-C18</x:f>
+        <x:v>-1.1368683772161603e-13</x:v>
+      </x:c>
+      <x:c r="E18" s="136" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:f>IF(ABS(D18)&lt;=E18,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>新来源独立数值控制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>2025末现金核对</x:v>
+      </x:c>
+      <x:c r="B19" s="136" t="n">
+        <x:f>'Segments'!H11</x:f>
+        <x:v>9.18626998261</x:v>
+      </x:c>
+      <x:c r="C19" s="136" t="n">
+        <x:v>9.18626998261</x:v>
+      </x:c>
+      <x:c r="D19" s="136" t="n">
+        <x:f>B19-C19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="136" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:f>IF(ABS(D19)&lt;=E19,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>新来源独立数值控制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>简化FCF核对</x:v>
+      </x:c>
+      <x:c r="B20" s="136" t="n">
+        <x:f>'Historical'!F21</x:f>
+        <x:v>5.10323557292</x:v>
+      </x:c>
+      <x:c r="C20" s="136" t="n">
+        <x:v>5.10323562998</x:v>
+      </x:c>
+      <x:c r="D20" s="136" t="n">
+        <x:f>B20-C20</x:f>
+        <x:v>-5.706000028027347e-8</x:v>
+      </x:c>
+      <x:c r="E20" s="136" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:f>IF(ABS(D20)&lt;=E20,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>新来源独立数值控制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>应付现金流核对</x:v>
+      </x:c>
+      <x:c r="B21" s="136" t="n">
+        <x:f>'Historical'!F22</x:f>
+        <x:v>1.9464313616</x:v>
+      </x:c>
+      <x:c r="C21" s="136" t="n">
+        <x:v>1.9464313616</x:v>
+      </x:c>
+      <x:c r="D21" s="136" t="n">
+        <x:f>B21-C21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="136" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:f>IF(ABS(D21)&lt;=E21,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>新来源独立数值控制</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3823,19 +4314,19 @@
         <x:v>A股收盘价</x:v>
       </x:c>
       <x:c r="C10" s="151" t="n">
-        <x:v>393</x:v>
+        <x:v>326.46</x:v>
       </x:c>
       <x:c r="D10" s="150" t="str">
         <x:v>RMB/股</x:v>
       </x:c>
       <x:c r="E10" s="150" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="F10" s="150" t="str">
         <x:v>历史行情</x:v>
       </x:c>
       <x:c r="G10" s="150" t="str">
-        <x:v>https://www.investing.com/equities/gigadevice-a-historical-data</x:v>
+        <x:v>https://cn.investing.com/equities/gigadevice-semiconductor-beijing-historical-data</x:v>
       </x:c>
       <x:c r="H10" s="150" t="str">
         <x:v>二级市场来源</x:v>
@@ -3855,13 +4346,13 @@
         <x:v>m shares</x:v>
       </x:c>
       <x:c r="E11" s="150" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-29确认</x:v>
       </x:c>
       <x:c r="F11" s="150" t="str">
-        <x:v>期权行权公告镜像</x:v>
+        <x:v>注册资本/股份登记公告</x:v>
       </x:c>
       <x:c r="G11" s="150" t="str">
-        <x:v>https://money.finance.sina.com.cn/corp/view/vCB_AllBulletinDetail.php?id=12550443&amp;stockid=603986</x:v>
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-9/2026-09-29/12623783.PDF</x:v>
       </x:c>
       <x:c r="H11" s="150" t="str">
         <x:v>原公告为上交所披露；A+H总股本</x:v>
@@ -3875,13 +4366,13 @@
         <x:v>Bear核心净利润</x:v>
       </x:c>
       <x:c r="C12" s="151" t="n">
-        <x:v>7.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="150" t="str">
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="E12" s="150" t="str">
-        <x:v>2026E</x:v>
+        <x:v>2027E</x:v>
       </x:c>
       <x:c r="F12" s="150" t="str">
         <x:v>分析假设</x:v>
@@ -3899,20 +4390,20 @@
         <x:v>Base核心净利润</x:v>
       </x:c>
       <x:c r="C13" s="151" t="n">
-        <x:v>10</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="D13" s="150" t="str">
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="E13" s="150" t="str">
-        <x:v>2026E</x:v>
+        <x:v>2027E</x:v>
       </x:c>
       <x:c r="F13" s="150" t="str">
         <x:v>分析假设</x:v>
       </x:c>
       <x:c r="G13" s="150" t="str"/>
       <x:c r="H13" s="150" t="str">
-        <x:v>H2隐含5.117bn</x:v>
+        <x:v>主估值85亿元；2026近期100亿元原假设另列</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
@@ -3929,7 +4420,7 @@
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="E14" s="150" t="str">
-        <x:v>2026E</x:v>
+        <x:v>2027E</x:v>
       </x:c>
       <x:c r="F14" s="150" t="str">
         <x:v>分析假设</x:v>
@@ -3951,7 +4442,7 @@
         <x:v>22x/30x/38x</x:v>
       </x:c>
       <x:c r="E15" s="150" t="str">
-        <x:v>2026E</x:v>
+        <x:v>2027E</x:v>
       </x:c>
       <x:c r="F15" s="150" t="str">
         <x:v>分析假设</x:v>
@@ -4008,7 +4499,7 @@
         <x:v>C2</x:v>
       </x:c>
       <x:c r="B18" s="152" t="str">
-        <x:v>经济股数</x:v>
+        <x:v>历史经济股数</x:v>
       </x:c>
       <x:c r="C18" s="153" t="n">
         <x:v>702.309127</x:v>
@@ -4027,9 +4518,174 @@
         <x:v>总股本减已回购拟注销股份</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="170" t="str">
+        <x:v>S7</x:v>
+      </x:c>
+      <x:c r="B20" s="170" t="str">
+        <x:v>2026年9月回购进展</x:v>
+      </x:c>
+      <x:c r="C20" s="170"/>
+      <x:c r="D20" s="170"/>
+      <x:c r="E20" s="170" t="str">
+        <x:v>2026-10-09</x:v>
+      </x:c>
+      <x:c r="F20" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G20" s="170" t="str">
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-10/2026-10-09/12632612.PDF</x:v>
+      </x:c>
+      <x:c r="H20" s="170" t="str">
+        <x:v>截至9月30日245.19万股、9.480124亿元，拟注销；每月数据不可当作含10月8日累计</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="58" customHeight="1">
+      <x:c r="A21" s="170" t="str">
+        <x:v>S8</x:v>
+      </x:c>
+      <x:c r="B21" s="170" t="str">
+        <x:v>长鑫采购额度增加及2027年前四月预算</x:v>
+      </x:c>
+      <x:c r="C21" s="170"/>
+      <x:c r="D21" s="170"/>
+      <x:c r="E21" s="170" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="F21" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G21" s="170" t="str">
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-9/2026-09-29/12623788.PDF</x:v>
+      </x:c>
+      <x:c r="H21" s="170" t="str">
+        <x:v>p1—3：2026预算57.11升78.54亿元、1—8月实际35.96、2027年1—4月预算44.11；不含税、尚待股东会；代工价格上升及新品解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="58" customHeight="1">
+      <x:c r="A22" s="170" t="str">
+        <x:v>S9</x:v>
+      </x:c>
+      <x:c r="B22" s="170" t="str">
+        <x:v>H股奖励授予公告</x:v>
+      </x:c>
+      <x:c r="C22" s="170"/>
+      <x:c r="D22" s="170"/>
+      <x:c r="E22" s="170" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="F22" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G22" s="170" t="str">
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-9/2026-09-29/12624731.PDF</x:v>
+      </x:c>
+      <x:c r="H22" s="170" t="str">
+        <x:v>授予148.79万份，1元人民币购买价，12/24/36/48个月各25%归属，非已发行股份；p4计划总授权7039.7142万股、余6890.9242万，基于A+H总股本10%，授权非确定新增</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="58" customHeight="1">
+      <x:c r="A23" s="170" t="str">
+        <x:v>S10</x:v>
+      </x:c>
+      <x:c r="B23" s="170" t="str">
+        <x:v>10月8日翌日披露报表</x:v>
+      </x:c>
+      <x:c r="C23" s="170"/>
+      <x:c r="D23" s="170"/>
+      <x:c r="E23" s="170" t="str">
+        <x:v>2026-10-08提交/10-09镜像</x:v>
+      </x:c>
+      <x:c r="F23" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G23" s="170" t="str">
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-10/2026-10-09/12633169.PDF</x:v>
+      </x:c>
+      <x:c r="H23" s="170" t="str">
+        <x:v>10月8日回购16.2万股、54,508,902.56元（PDF p5已目视核验），A股670,718,327股未变；已回购股份尚未注销</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="58" customHeight="1">
+      <x:c r="A24" s="170" t="str">
+        <x:v>S11</x:v>
+      </x:c>
+      <x:c r="B24" s="170" t="str">
+        <x:v>注册资本与章程调整公告</x:v>
+      </x:c>
+      <x:c r="C24" s="170"/>
+      <x:c r="D24" s="170"/>
+      <x:c r="E24" s="170" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="F24" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G24" s="170" t="str">
+        <x:v>https://file.finance.sina.com.cn/211.154.219.97%3A9494/MRGG/CNSESH_STOCK/2026/2026-9/2026-09-29/12623783.PDF</x:v>
+      </x:c>
+      <x:c r="H24" s="170" t="str">
+        <x:v>A股670,718,327+H股33,253,100=703,971,427股；注册资本及章程修改尚待股东会，不否定已完成股份登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="170" t="str">
+        <x:v>S12</x:v>
+      </x:c>
+      <x:c r="B25" s="170" t="str">
+        <x:v>A股历史行情研究快照</x:v>
+      </x:c>
+      <x:c r="C25" s="170"/>
+      <x:c r="D25" s="170"/>
+      <x:c r="E25" s="170" t="str">
+        <x:v>价格2026-10-09/检索2026-10-12午间</x:v>
+      </x:c>
+      <x:c r="F25" s="170" t="str">
+        <x:v>公司公告原件/市场快照</x:v>
+      </x:c>
+      <x:c r="G25" s="170" t="str">
+        <x:v>https://cn.investing.com/equities/gigadevice-semiconductor-beijing-historical-data</x:v>
+      </x:c>
+      <x:c r="H25" s="170" t="str">
+        <x:v>10月9日收盘326.46元；10月12日页面为延迟日内价，本报告不称当日收盘；本次未给H股当前目标价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="172" t="str">
+        <x:v>2027利润/投资/P-E为研究假设；已授予奖励全额新增为压力口径，计划授权70.397142m仅做敏感性。H1期初现金改为9.18626998bn。普通回购尚未注销，不与2021限制性股票已注销4565股混用。</x:v>
+      </x:c>
+      <x:c r="B28" s="172"/>
+      <x:c r="C28" s="172"/>
+      <x:c r="D28" s="172"/>
+      <x:c r="E28" s="172"/>
+      <x:c r="F28" s="172"/>
+      <x:c r="G28" s="172"/>
+      <x:c r="H28" s="172"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="172"/>
+      <x:c r="B29" s="172"/>
+      <x:c r="C29" s="172"/>
+      <x:c r="D29" s="172"/>
+      <x:c r="E29" s="172"/>
+      <x:c r="F29" s="172"/>
+      <x:c r="G29" s="172"/>
+      <x:c r="H29" s="172"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="172"/>
+      <x:c r="B30" s="172"/>
+      <x:c r="C30" s="172"/>
+      <x:c r="D30" s="172"/>
+      <x:c r="E30" s="172"/>
+      <x:c r="F30" s="172"/>
+      <x:c r="G30" s="172"/>
+      <x:c r="H30" s="172"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A28:H30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
